--- a/research/traditional_assets/database/data/netherlands/netherlands_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_drugs_pharmaceutical.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-45.3</v>
+        <v>-48.5</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +612,58 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>266</v>
+        <v>193.9</v>
       </c>
       <c r="V2">
-        <v>0.5580029368575624</v>
-      </c>
-      <c r="W2">
-        <v>-2.220588235294118</v>
+        <v>0.5101289134438306</v>
       </c>
       <c r="X2">
-        <v>0.05590681033591963</v>
-      </c>
-      <c r="Y2">
-        <v>-2.276495045630037</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>-2.347486578818936</v>
+        <v>0.09780832811883358</v>
       </c>
       <c r="AB2">
-        <v>0.05588360898572299</v>
-      </c>
-      <c r="AC2">
-        <v>-2.403370187804659</v>
+        <v>0.09778054744334962</v>
       </c>
       <c r="AD2">
-        <v>0.339</v>
+        <v>0.195</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.339</v>
+        <v>0.195</v>
       </c>
       <c r="AG2">
-        <v>-265.661</v>
+        <v>-193.705</v>
       </c>
       <c r="AH2">
-        <v>0.000710633721771176</v>
+        <v>0.0005127598311836863</v>
       </c>
       <c r="AI2">
-        <v>0.001284874487850545</v>
+        <v>0.001072636761187051</v>
       </c>
       <c r="AJ2">
-        <v>-1.258824198370917</v>
+        <v>-1.039217790176775</v>
       </c>
       <c r="AK2">
-        <v>122.9342896807033</v>
+        <v>16.00206526228829</v>
       </c>
       <c r="AL2">
-        <v>0.109</v>
+        <v>0.147</v>
       </c>
       <c r="AM2">
-        <v>0.109</v>
+        <v>0.147</v>
       </c>
       <c r="AN2">
-        <v>-0.007047817047817048</v>
+        <v>-0.002506426735218509</v>
       </c>
       <c r="AO2">
-        <v>-441.2844036697248</v>
+        <v>-529.2517006802722</v>
       </c>
       <c r="AP2">
-        <v>5.523097713097713</v>
+        <v>2.489781491002571</v>
       </c>
       <c r="AQ2">
-        <v>-441.2844036697248</v>
+        <v>-529.2517006802722</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +683,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-45.3</v>
+        <v>-48.5</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,73 +707,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>266</v>
+        <v>193.9</v>
       </c>
       <c r="V3">
-        <v>0.5580029368575624</v>
-      </c>
-      <c r="W3">
-        <v>-2.220588235294118</v>
+        <v>0.5101289134438306</v>
       </c>
       <c r="X3">
-        <v>0.05590681033591963</v>
-      </c>
-      <c r="Y3">
-        <v>-2.276495045630037</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>-2.347486578818936</v>
+        <v>0.09780832811883358</v>
       </c>
       <c r="AB3">
-        <v>0.05588360898572299</v>
-      </c>
-      <c r="AC3">
-        <v>-2.403370187804659</v>
+        <v>0.09778054744334962</v>
       </c>
       <c r="AD3">
-        <v>0.339</v>
+        <v>0.195</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.339</v>
+        <v>0.195</v>
       </c>
       <c r="AG3">
-        <v>-265.661</v>
+        <v>-193.705</v>
       </c>
       <c r="AH3">
-        <v>0.000710633721771176</v>
+        <v>0.0005127598311836863</v>
       </c>
       <c r="AI3">
-        <v>0.001284874487850545</v>
+        <v>0.001072636761187051</v>
       </c>
       <c r="AJ3">
-        <v>-1.258824198370917</v>
+        <v>-1.039217790176775</v>
       </c>
       <c r="AK3">
-        <v>122.9342896807033</v>
+        <v>16.00206526228829</v>
       </c>
       <c r="AL3">
-        <v>0.109</v>
+        <v>0.147</v>
       </c>
       <c r="AM3">
-        <v>0.109</v>
+        <v>0.147</v>
       </c>
       <c r="AN3">
-        <v>-0.007047817047817048</v>
+        <v>-0.002506426735218509</v>
       </c>
       <c r="AO3">
-        <v>-441.2844036697248</v>
+        <v>-529.2517006802722</v>
       </c>
       <c r="AP3">
-        <v>5.523097713097713</v>
+        <v>2.489781491002571</v>
       </c>
       <c r="AQ3">
-        <v>-441.2844036697248</v>
+        <v>-529.2517006802722</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_drugs_pharmaceutical.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-48.5</v>
+        <v>-113.6</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,58 +612,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>193.9</v>
+        <v>167.6</v>
       </c>
       <c r="V2">
-        <v>0.5101289134438306</v>
+        <v>0.1146688560481664</v>
+      </c>
+      <c r="W2">
+        <v>-0.6255506607929515</v>
       </c>
       <c r="X2">
-        <v>0.09780832811883358</v>
+        <v>0.07947607739389861</v>
+      </c>
+      <c r="Y2">
+        <v>-0.7050267381868501</v>
       </c>
       <c r="AB2">
-        <v>0.09778054744334962</v>
+        <v>0.07946770034761846</v>
       </c>
       <c r="AD2">
-        <v>0.195</v>
+        <v>0.308</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.195</v>
+        <v>0.308</v>
       </c>
       <c r="AG2">
-        <v>-193.705</v>
+        <v>-167.292</v>
       </c>
       <c r="AH2">
-        <v>0.0005127598311836863</v>
+        <v>0.0002106835724272663</v>
       </c>
       <c r="AI2">
-        <v>0.001072636761187051</v>
+        <v>0.001896458302546673</v>
       </c>
       <c r="AJ2">
-        <v>-1.039217790176775</v>
+        <v>-0.1292520791032737</v>
       </c>
       <c r="AK2">
-        <v>16.00206526228829</v>
+        <v>32.22110939907546</v>
       </c>
       <c r="AL2">
-        <v>0.147</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.147</v>
+        <v>-0.265</v>
       </c>
       <c r="AN2">
-        <v>-0.002506426735218509</v>
-      </c>
-      <c r="AO2">
-        <v>-529.2517006802722</v>
+        <v>-0.003117408906882591</v>
       </c>
       <c r="AP2">
-        <v>2.489781491002571</v>
+        <v>1.693238866396761</v>
       </c>
       <c r="AQ2">
-        <v>-529.2517006802722</v>
+        <v>372.8301886792453</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +686,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-48.5</v>
+        <v>-113.6</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -707,58 +710,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>193.9</v>
+        <v>167.6</v>
       </c>
       <c r="V3">
-        <v>0.5101289134438306</v>
+        <v>0.1146688560481664</v>
+      </c>
+      <c r="W3">
+        <v>-0.6255506607929515</v>
       </c>
       <c r="X3">
-        <v>0.09780832811883358</v>
+        <v>0.07947607739389861</v>
+      </c>
+      <c r="Y3">
+        <v>-0.7050267381868501</v>
       </c>
       <c r="AB3">
-        <v>0.09778054744334962</v>
+        <v>0.07946770034761846</v>
       </c>
       <c r="AD3">
-        <v>0.195</v>
+        <v>0.308</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.195</v>
+        <v>0.308</v>
       </c>
       <c r="AG3">
-        <v>-193.705</v>
+        <v>-167.292</v>
       </c>
       <c r="AH3">
-        <v>0.0005127598311836863</v>
+        <v>0.0002106835724272663</v>
       </c>
       <c r="AI3">
-        <v>0.001072636761187051</v>
+        <v>0.001896458302546673</v>
       </c>
       <c r="AJ3">
-        <v>-1.039217790176775</v>
+        <v>-0.1292520791032737</v>
       </c>
       <c r="AK3">
-        <v>16.00206526228829</v>
+        <v>32.22110939907546</v>
       </c>
       <c r="AL3">
-        <v>0.147</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.147</v>
+        <v>-0.265</v>
       </c>
       <c r="AN3">
-        <v>-0.002506426735218509</v>
-      </c>
-      <c r="AO3">
-        <v>-529.2517006802722</v>
+        <v>-0.003117408906882591</v>
       </c>
       <c r="AP3">
-        <v>2.489781491002571</v>
+        <v>1.693238866396761</v>
       </c>
       <c r="AQ3">
-        <v>-529.2517006802722</v>
+        <v>372.8301886792453</v>
       </c>
     </row>
   </sheetData>
